--- a/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260916095454</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}

--- a/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$63</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="436">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -435,33 +435,57 @@
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:composition</t>
+  </si>
+  <si>
+    <t>composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Composition du rapport de biologie</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -469,6 +493,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -517,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -582,17 +609,51 @@
 Sub-departmentServiceDiscipline</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Catégorie du rapport de biologie</t>
+    <t>Type de résultat</t>
   </si>
   <si>
     <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:typeResultat</t>
+  </si>
+  <si>
+    <t>typeResultat</t>
+  </si>
+  <si>
+    <t>Type de résultat de biologie</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -604,25 +665,12 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260916095454</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:chapitreBIO</t>
   </si>
   <si>
@@ -632,7 +680,7 @@
     <t>Codes des chapitres du compte-rendu de BIO</t>
   </si>
   <si>
-    <t>Le code du chapitre doit être un code issu du jeu de valeurs Circuit de la biologie (disponible sur bioloinc.fr), onglet ‘2.Chapitres LOINC’ et contenant les codes et libellés traduits en français pour la biologie.</t>
+    <t>Le code du chapitre doit être issu du jeu de valeurs Circuit de la biologie (https://smt.esante.gouv.fr/terminologie-jeu-de-valeurs-circuit-de-la-biologie/) onglet ‘2.Chapitres LOINC’ et contenant les codes et libellés traduits en français pour la biologie.</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -648,6 +696,15 @@
     <t>A code or name that describes this diagnostic report.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="11502-2"/&gt;
+    &lt;display value="CR d'examens biologiques"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
@@ -849,7 +906,7 @@
 </t>
   </si>
   <si>
-    <t>Organization productrice du CR de biologie</t>
+    <t>Organization productrice du CR</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -893,16 +950,6 @@
     <t>DiagnosticReport.resultsInterpreter.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
@@ -937,9 +984,6 @@
     <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type</t>
   </si>
   <si>
@@ -1089,9 +1133,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -1238,6 +1279,9 @@
     <t>DiagnosticReport.media.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -1321,9 +1365,6 @@
   </si>
   <si>
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
@@ -1671,12 +1712,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.1484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2642,11 +2683,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2661,17 +2702,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2708,16 +2747,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -2741,54 +2778,52 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2836,7 +2871,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2845,7 +2880,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -2857,7 +2892,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -2865,14 +2900,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2885,13 +2920,13 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>150</v>
@@ -2952,7 +2987,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2964,31 +2999,31 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3004,22 +3039,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3068,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3083,47 +3118,47 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>169</v>
@@ -3131,9 +3166,11 @@
       <c r="M13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3143,7 +3180,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -3158,13 +3195,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3182,13 +3219,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3197,58 +3234,58 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM13" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3257,7 +3294,7 @@
         <v>80</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>80</v>
@@ -3272,33 +3309,37 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3307,34 +3348,32 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>79</v>
@@ -3349,16 +3388,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3384,29 +3423,29 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3424,25 +3463,27 @@
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3452,7 +3493,7 @@
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>80</v>
@@ -3461,15 +3502,17 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3479,7 +3522,7 @@
         <v>80</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>80</v>
@@ -3494,13 +3537,11 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3518,13 +3559,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -3533,35 +3574,37 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>91</v>
@@ -3573,7 +3616,7 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>209</v>
@@ -3581,10 +3624,10 @@
       <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="N17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3608,13 +3651,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3632,13 +3675,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3647,32 +3690,32 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
@@ -3687,20 +3730,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3709,7 +3748,7 @@
         <v>80</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>80</v>
@@ -3724,13 +3763,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3748,10 +3787,10 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>90</v>
@@ -3763,28 +3802,28 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3803,19 +3842,17 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3864,7 +3901,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3879,28 +3916,28 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3910,7 +3947,7 @@
         <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -3919,19 +3956,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3980,7 +4017,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3995,35 +4032,35 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>91</v>
@@ -4035,19 +4072,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4084,23 +4121,25 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -4109,40 +4148,38 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
@@ -4151,19 +4188,19 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4212,13 +4249,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -4227,19 +4264,19 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>264</v>
       </c>
@@ -4267,19 +4304,19 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4316,16 +4353,14 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>264</v>
@@ -4343,35 +4378,37 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4380,19 +4417,23 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4440,71 +4481,75 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
-      </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4540,19 +4585,19 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4564,40 +4609,38 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>80</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4609,13 +4652,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4666,19 +4709,19 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -4687,7 +4730,7 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -4695,10 +4738,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4706,10 +4749,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -4721,13 +4764,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4766,31 +4809,31 @@
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -4799,7 +4842,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4807,18 +4850,20 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>291</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -4833,13 +4878,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4878,19 +4923,19 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4919,20 +4964,18 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
@@ -4947,13 +4990,13 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5004,19 +5047,19 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5025,7 +5068,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5033,10 +5076,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5044,10 +5087,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5059,13 +5102,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5104,31 +5147,31 @@
         <v>80</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5137,7 +5180,7 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5145,21 +5188,23 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5171,13 +5216,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5216,19 +5261,19 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5257,10 +5302,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5268,7 +5313,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
@@ -5283,24 +5328,22 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -5342,10 +5385,10 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5363,7 +5406,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5371,10 +5414,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5385,7 +5428,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5397,13 +5440,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5415,7 +5458,7 @@
         <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>80</v>
@@ -5430,41 +5473,43 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>309</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5473,7 +5518,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5481,20 +5526,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>312</v>
-      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5509,22 +5552,24 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -5566,19 +5611,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5587,7 +5632,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5595,10 +5640,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5621,13 +5666,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5639,7 +5684,7 @@
         <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>80</v>
@@ -5654,13 +5699,11 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -5678,7 +5721,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5690,7 +5733,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5699,7 +5742,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5707,12 +5750,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5721,7 +5766,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -5733,13 +5778,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5778,19 +5823,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5819,10 +5864,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5830,7 +5875,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
@@ -5845,24 +5890,22 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -5904,10 +5947,10 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>90</v>
@@ -5925,7 +5968,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5933,10 +5976,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5947,7 +5990,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -5959,13 +6002,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6004,31 +6047,31 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6037,7 +6080,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6045,14 +6088,12 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6073,22 +6114,24 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>80</v>
@@ -6130,19 +6173,19 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6151,7 +6194,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6159,10 +6202,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6185,13 +6228,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6242,7 +6285,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6254,7 +6297,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6263,7 +6306,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6271,21 +6314,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6297,13 +6342,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6342,19 +6387,19 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6383,10 +6428,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6394,7 +6439,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -6409,24 +6454,22 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>80</v>
@@ -6468,10 +6511,10 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6489,7 +6532,7 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6497,10 +6540,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6511,7 +6554,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -6523,13 +6566,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6568,31 +6611,31 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -6601,7 +6644,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -6609,10 +6652,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6638,13 +6681,13 @@
         <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6652,7 +6695,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>80</v>
@@ -6694,7 +6737,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>90</v>
@@ -6723,10 +6766,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6737,7 +6780,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6749,13 +6792,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6806,7 +6849,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6835,10 +6878,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6846,7 +6889,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -6858,19 +6901,19 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6878,7 +6921,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>80</v>
@@ -6920,19 +6963,19 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -6949,10 +6992,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6963,7 +7006,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -6972,20 +7015,18 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>342</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7010,13 +7051,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7034,7 +7075,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7063,10 +7104,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7089,16 +7130,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>149</v>
+        <v>287</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7148,7 +7189,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7157,7 +7198,7 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
@@ -7169,7 +7210,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7177,10 +7218,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7203,16 +7244,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7238,13 +7279,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7289,7 +7330,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>356</v>
       </c>
@@ -7305,32 +7346,30 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K50" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>361</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7378,13 +7417,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7396,57 +7435,55 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K51" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>369</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7494,13 +7531,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7512,21 +7549,21 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>370</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>371</v>
+        <v>133</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7540,7 +7577,7 @@
         <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -7549,18 +7586,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7608,7 +7647,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7626,10 +7665,10 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>230</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7637,18 +7676,18 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>79</v>
@@ -7660,20 +7699,22 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7722,7 +7763,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7740,10 +7781,10 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7751,10 +7792,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7765,7 +7806,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -7777,15 +7818,17 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>271</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>272</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -7834,19 +7877,19 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>274</v>
+        <v>383</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -7855,22 +7898,22 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>390</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7880,27 +7923,27 @@
         <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>391</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -7948,7 +7991,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>281</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7960,16 +8003,16 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>275</v>
+        <v>382</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -7977,46 +8020,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>288</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8064,19 +8103,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>290</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8085,7 +8124,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8093,21 +8132,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8119,20 +8158,18 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8180,19 +8217,19 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>294</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -8201,50 +8238,54 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>398</v>
+        <v>291</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8292,19 +8333,19 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -8313,22 +8354,22 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>403</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8338,7 +8379,7 @@
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -8347,7 +8388,7 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>406</v>
@@ -8355,9 +8396,11 @@
       <c r="M59" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8406,7 +8449,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8424,7 +8467,7 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>410</v>
@@ -8433,7 +8476,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>411</v>
       </c>
@@ -8446,28 +8489,28 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>181</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8494,13 +8537,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8521,10 +8564,10 @@
         <v>411</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -8536,10 +8579,10 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8547,18 +8590,18 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
@@ -8573,19 +8616,17 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -8634,13 +8675,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -8652,17 +8693,245 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="M62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN61">
+  <autoFilter ref="A1:AN63">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8672,7 +8941,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
